--- a/Student Performance Analysis.xlsx
+++ b/Student Performance Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2044c300c19afe8e/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="705" documentId="13_ncr:1_{9ED5D69B-7B86-4441-8593-32CC23443D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F7FA83E-8C49-4961-9D4E-0AF9AA93619A}"/>
+  <xr:revisionPtr revIDLastSave="863" documentId="13_ncr:1_{9ED5D69B-7B86-4441-8593-32CC23443D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7197C1C7-A7B8-40C6-8328-3601534A075F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="9" xr2:uid="{45F2EF41-DCCC-41AF-BAC2-A90508D60E03}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="884" xr2:uid="{45F2EF41-DCCC-41AF-BAC2-A90508D60E03}"/>
   </bookViews>
   <sheets>
     <sheet name="Pivot_Stress" sheetId="5" r:id="rId1"/>
@@ -19,15 +19,15 @@
     <sheet name="Pivot_Health" sheetId="15" r:id="rId4"/>
     <sheet name="Pivot_Tution" sheetId="16" r:id="rId5"/>
     <sheet name="Pivot_DailyWork" sheetId="17" r:id="rId6"/>
-    <sheet name="Cleaned_Data" sheetId="3" r:id="rId7"/>
-    <sheet name="Report" sheetId="7" r:id="rId8"/>
+    <sheet name="DashBoard" sheetId="18" r:id="rId7"/>
+    <sheet name="Cleaned_Data" sheetId="3" r:id="rId8"/>
     <sheet name="Analysis" sheetId="4" r:id="rId9"/>
     <sheet name="Raw_Data(Original)" sheetId="1" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="10" r:id="rId11"/>
-    <pivotCache cacheId="20" r:id="rId12"/>
+    <pivotCache cacheId="0" r:id="rId11"/>
+    <pivotCache cacheId="1" r:id="rId12"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="70">
   <si>
     <t>NAME</t>
   </si>
@@ -214,9 +214,6 @@
     <t>Lowest Exam Score</t>
   </si>
   <si>
-    <t>Avergae Self Study</t>
-  </si>
-  <si>
     <t>Row Labels</t>
   </si>
   <si>
@@ -226,67 +223,10 @@
     <t>Average of EXAM SCORE</t>
   </si>
   <si>
-    <t>Student Performance Analysis Report</t>
-  </si>
-  <si>
-    <t>Project Objective</t>
-  </si>
-  <si>
-    <t>To analyze the student performance data and identify the factors affecting the academic results using Microsoft Excel and SQL.</t>
-  </si>
-  <si>
-    <t>Dataset Information</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Total Columns</t>
-  </si>
-  <si>
-    <t>Missing Values</t>
-  </si>
-  <si>
-    <t>Duplicate Records</t>
-  </si>
-  <si>
-    <t>Invalid Values</t>
-  </si>
-  <si>
-    <t>Data Cleaning Performed</t>
-  </si>
-  <si>
-    <t>&gt; Filled numeric missing values using average</t>
-  </si>
-  <si>
-    <t>&gt; Identified 6 missing values</t>
-  </si>
-  <si>
-    <t>&gt; Removed duplicate data (None found)</t>
-  </si>
-  <si>
-    <t>&gt; Filled categorical missing values using mode</t>
-  </si>
-  <si>
-    <t>&gt; Standardized data for analysis</t>
-  </si>
-  <si>
-    <t>KPI Summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPI </t>
-  </si>
-  <si>
     <t>Highest Exam Score</t>
   </si>
   <si>
     <t>Average Self Study</t>
-  </si>
-  <si>
-    <t>Analysis Completed</t>
   </si>
   <si>
     <t>ATTENDANCE GROUP</t>
@@ -299,6 +239,113 @@
   </si>
   <si>
     <t>Poor (&lt;60%)</t>
+  </si>
+  <si>
+    <t>Student Performance Analysis Dashboard</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Students with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">High Attendance </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>scored high average marks then poor attendance</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">More </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Self Study hours </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>associated with better academic performance</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Students with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Good Health </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>achieved hig scores than the students with poor health</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Students with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Low Stress</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Level is achieving high average score</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -452,7 +499,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -632,8 +679,32 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -763,6 +834,89 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -808,7 +962,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -827,24 +981,84 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="16" fillId="35" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="16" fillId="35" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="35" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="35" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="4"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="36" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="36" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="36" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="36" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="36" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="36" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="36" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="36" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -927,7 +1141,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[STUDENT 1.xlsx]Pivot_Stress!PivotTable1</c:name>
+    <c:name>[Student Performance Analysis.xlsx]Pivot_Stress!PivotTable1</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
@@ -1427,6 +1641,626 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Student Performance Analysis.xlsx]Pivot_Health!PivotTable8</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Average</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1" baseline="0"/>
+              <a:t> Exam Score by Health Status</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" b="1"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Pivot_Health!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Pivot_Health!$A$4:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>BAD</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>GOOD</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Pivot_Health!$B$4:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>65.15384615384616</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>89.411764705882348</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-065F-4748-B66B-2F13164F9AA1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1414041263"/>
+        <c:axId val="1360820671"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1414041263"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1"/>
+                  <a:t>Health</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1" baseline="0"/>
+                  <a:t> Status</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-IN" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-IN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1360820671"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1360820671"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1"/>
+                  <a:t>Average</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1" baseline="0"/>
+                  <a:t> Exam Score</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-IN" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-IN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1414041263"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -1441,7 +2275,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[STUDENT 1.xlsx]Pivot_Self Study!PivotTable2</c:name>
+    <c:name>[Student Performance Analysis.xlsx]Pivot_Self Study!PivotTable2</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
@@ -1501,7 +2335,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-IN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1723,7 +2557,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-IN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1848,7 +2682,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-IN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1967,7 +2801,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[STUDENT 1.xlsx]Pivot_Attendance!PivotTable7</c:name>
+    <c:name>[Student Performance Analysis.xlsx]Pivot_Attendance!PivotTable7</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
@@ -2027,7 +2861,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-IN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2237,7 +3071,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-IN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2362,7 +3196,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-IN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2481,7 +3315,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[STUDENT 1.xlsx]Pivot_Health!PivotTable8</c:name>
+    <c:name>[Student Performance Analysis.xlsx]Pivot_Health!PivotTable8</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
@@ -2745,7 +3579,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-IN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2870,7 +3704,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-IN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2989,7 +3823,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[STUDENT 1.xlsx]Pivot_Tution!PivotTable9</c:name>
+    <c:name>[Student Performance Analysis.xlsx]Pivot_Tution!PivotTable9</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
@@ -3253,7 +4087,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-IN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3378,7 +4212,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-IN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3497,7 +4331,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[STUDENT 1.xlsx]Pivot_DailyWork!PivotTable10</c:name>
+    <c:name>[Student Performance Analysis.xlsx]Pivot_DailyWork!PivotTable10</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
@@ -3557,7 +4391,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-IN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3767,7 +4601,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-IN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3892,7 +4726,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-IN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3997,7 +4831,1937 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Student Performance Analysis.xlsx]Pivot_Stress!PivotTable1</c:name>
+    <c:fmtId val="5"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" b="1"/>
+              <a:t>Average</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-IN" b="1" baseline="0"/>
+              <a:t> Exam Score By Stress Level</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN" b="1"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-IN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Pivot_Stress!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Pivot_Stress!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>HIGH</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>LOW</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>MODERATE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Pivot_Stress!$B$4:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>58.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>93.6875</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>75.666666666666671</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CACF-4A23-A477-AF258C3B88AC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="446675456"/>
+        <c:axId val="70317632"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="446675456"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1"/>
+                  <a:t>Stress</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1" baseline="0"/>
+                  <a:t> Level</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-IN" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-IN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="70317632"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="70317632"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1"/>
+                  <a:t>Average</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1" baseline="0"/>
+                  <a:t> Exam Score</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-IN" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-IN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="446675456"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Student Performance Analysis.xlsx]Pivot_Self Study!PivotTable2</c:name>
+    <c:fmtId val="5"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" b="1"/>
+              <a:t>Average</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-IN" b="1" baseline="0"/>
+              <a:t> Exam Score by Self Study</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN" b="1"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-IN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Pivot_Self Study'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pivot_Self Study'!$A$4:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pivot_Self Study'!$B$4:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>58.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>75.666666666666671</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>89.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>97</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9674-41B0-A893-192487FB6016}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1297920255"/>
+        <c:axId val="1227406015"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1297920255"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1"/>
+                  <a:t>Self</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1" baseline="0"/>
+                  <a:t> Study Hours</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-IN" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-IN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1227406015"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1227406015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1"/>
+                  <a:t>Average</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1" baseline="0"/>
+                  <a:t> Exam Score</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-IN" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-IN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1297920255"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Student Performance Analysis.xlsx]Pivot_Attendance!PivotTable7</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" b="1"/>
+              <a:t>Average</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-IN" b="1" baseline="0"/>
+              <a:t> Exam Score by Attendance Group</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN" b="1"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-IN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Pivot_Attendance!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Pivot_Attendance!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Poor (&lt;60%)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Average (60 - 79%)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Good (80 - 100%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Pivot_Attendance!$B$4:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>72.875</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>90.875</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-71CE-4A98-828E-FB7F98D33962}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1355658703"/>
+        <c:axId val="1360819711"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1355658703"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1"/>
+                  <a:t>Attendance</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1" baseline="0"/>
+                  <a:t> Group</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-IN" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-IN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1360819711"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1360819711"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1"/>
+                  <a:t>Average</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1" baseline="0"/>
+                  <a:t> Exam Score</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-IN" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-IN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1355658703"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -4237,6 +7001,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -4740,7 +7624,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5243,7 +8127,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5746,7 +8630,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6249,7 +9133,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6752,7 +9636,2019 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7499,6 +12395,167 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>26377</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>128954</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>26377</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>163244</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B809CD2-9F82-4848-A193-74448D89BC7F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>32238</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>46892</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>32238</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>84992</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{877D6EC8-05EB-4B0B-BC56-D45BF84DF5E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>103163</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>140091</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7720C711-A9DA-4B0C-8D61-DBFFBC061788}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>16999</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>73855</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>16999</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>95543</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{266467A5-C075-479B-8283-5F4992E53AC6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8416,7 +13473,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D7CC4C59-7347-4F9A-B2A3-6A8D1D26DA91}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D7CC4C59-7347-4F9A-B2A3-6A8D1D26DA91}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -8490,8 +13547,17 @@
       </pivotArea>
     </format>
   </formats>
-  <chartFormats count="1">
+  <chartFormats count="2">
     <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -8514,7 +13580,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BA38A7D2-7FEE-4494-A1F5-7ECB06E1537B}" name="PivotTable2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BA38A7D2-7FEE-4494-A1F5-7ECB06E1537B}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -8567,8 +13633,17 @@
   <dataFields count="1">
     <dataField name="Average of EXAM SCORE" fld="3" subtotal="average" baseField="9" baseItem="0" numFmtId="164"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="2">
     <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -8591,7 +13666,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3322CD0B-F693-4059-AE87-26F402BF334C}" name="PivotTable7" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3322CD0B-F693-4059-AE87-26F402BF334C}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -8636,8 +13711,17 @@
   <dataFields count="1">
     <dataField name="Average of EXAM SCORE" fld="4" subtotal="average" baseField="3" baseItem="0" numFmtId="164"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="2">
     <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -8660,7 +13744,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3488BF17-8DC2-47E3-9F6D-887400036A17}" name="PivotTable8" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3488BF17-8DC2-47E3-9F6D-887400036A17}" name="PivotTable8" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -8701,8 +13785,17 @@
   <dataFields count="1">
     <dataField name="Average of EXAM SCORE" fld="4" subtotal="average" baseField="7" baseItem="0" numFmtId="164"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="2">
     <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -8725,7 +13818,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A48A15B9-DCAC-4ACB-B476-BFD8CBCCCB20}" name="PivotTable9" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A48A15B9-DCAC-4ACB-B476-BFD8CBCCCB20}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -8790,7 +13883,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6A160FFA-9CE8-4CE2-B0B6-7955D5577F02}" name="PivotTable10" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6A160FFA-9CE8-4CE2-B0B6-7955D5577F02}" name="PivotTable10" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -9164,10 +14257,10 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -9196,7 +14289,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7">
         <v>78.900000000000006</v>
@@ -10214,17 +15307,17 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>0</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="10">
         <v>58.272727272727273</v>
       </c>
     </row>
@@ -10232,7 +15325,7 @@
       <c r="A5" s="8">
         <v>2</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="10">
         <v>75.666666666666671</v>
       </c>
     </row>
@@ -10240,7 +15333,7 @@
       <c r="A6" s="8">
         <v>3.5</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="10">
         <v>82</v>
       </c>
     </row>
@@ -10248,7 +15341,7 @@
       <c r="A7" s="8">
         <v>4</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="10">
         <v>89.4</v>
       </c>
     </row>
@@ -10256,15 +15349,15 @@
       <c r="A8" s="8">
         <v>5</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="10">
         <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="17">
+        <v>57</v>
+      </c>
+      <c r="B9" s="10">
         <v>78.900000000000006</v>
       </c>
     </row>
@@ -10285,41 +15378,41 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B4" s="17">
+        <v>64</v>
+      </c>
+      <c r="B4" s="10">
         <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" s="17">
+        <v>62</v>
+      </c>
+      <c r="B5" s="10">
         <v>72.875</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" s="17">
+        <v>63</v>
+      </c>
+      <c r="B6" s="10">
         <v>90.875</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="17">
+        <v>57</v>
+      </c>
+      <c r="B7" s="10">
         <v>78.900000000000006</v>
       </c>
     </row>
@@ -10340,17 +15433,17 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="10">
         <v>65.15384615384616</v>
       </c>
     </row>
@@ -10358,15 +15451,15 @@
       <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="10">
         <v>89.411764705882348</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="17">
+        <v>57</v>
+      </c>
+      <c r="B6" s="10">
         <v>78.900000000000006</v>
       </c>
     </row>
@@ -10387,17 +15480,17 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="10">
         <v>87.611111111111114</v>
       </c>
     </row>
@@ -10405,15 +15498,15 @@
       <c r="A5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="10">
         <v>65.833333333333329</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="17">
+        <v>57</v>
+      </c>
+      <c r="B6" s="10">
         <v>78.900000000000006</v>
       </c>
     </row>
@@ -10434,17 +15527,17 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="10">
         <v>58.272727272727273</v>
       </c>
     </row>
@@ -10452,7 +15545,7 @@
       <c r="A5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="10">
         <v>75.666666666666671</v>
       </c>
     </row>
@@ -10460,15 +15553,15 @@
       <c r="A6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="10">
         <v>93.6875</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="17">
+        <v>57</v>
+      </c>
+      <c r="B7" s="10">
         <v>78.900000000000006</v>
       </c>
     </row>
@@ -10479,6 +15572,222 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{702D800A-C5D4-42E5-B8DE-93B2E7A7E480}">
+  <dimension ref="A1:R55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="D4" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="18"/>
+      <c r="H4" s="14"/>
+    </row>
+    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="29"/>
+      <c r="B5" s="30"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="32"/>
+    </row>
+    <row r="6" spans="1:8" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="26">
+        <f>Analysis!B1</f>
+        <v>30</v>
+      </c>
+      <c r="B6" s="27"/>
+      <c r="D6" s="24">
+        <f>Analysis!B2</f>
+        <v>19.766666666666666</v>
+      </c>
+      <c r="E6" s="25"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="D8" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="20"/>
+    </row>
+    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="31"/>
+      <c r="B9" s="32"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="30"/>
+    </row>
+    <row r="10" spans="1:8" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="24">
+        <f>Analysis!B3</f>
+        <v>77.566666666666663</v>
+      </c>
+      <c r="B10" s="25"/>
+      <c r="D10" s="28">
+        <f>Analysis!B4</f>
+        <v>78.900000000000006</v>
+      </c>
+      <c r="E10" s="27"/>
+    </row>
+    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="D12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="16"/>
+    </row>
+    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="29"/>
+      <c r="B13" s="30"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="30"/>
+    </row>
+    <row r="14" spans="1:8" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="26">
+        <f>Analysis!B5</f>
+        <v>100</v>
+      </c>
+      <c r="B14" s="27"/>
+      <c r="D14" s="26">
+        <f>Analysis!B6</f>
+        <v>40</v>
+      </c>
+      <c r="E14" s="27"/>
+    </row>
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G15" s="39"/>
+    </row>
+    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="23"/>
+    </row>
+    <row r="17" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="36"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="38"/>
+    </row>
+    <row r="18" spans="2:4" ht="24" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="33">
+        <f>Analysis!B7</f>
+        <v>2.65</v>
+      </c>
+      <c r="C18" s="34"/>
+      <c r="D18" s="35"/>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A37" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="K37" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="11"/>
+      <c r="P37" s="11"/>
+      <c r="Q37" s="11"/>
+      <c r="R37" s="11"/>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A55" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
+      <c r="K55" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="11"/>
+      <c r="O55" s="11"/>
+      <c r="P55" s="11"/>
+      <c r="Q55" s="11"/>
+      <c r="R55" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="26">
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="K55:R55"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="K37:R37"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47FCC87E-6629-46F7-B610-7ED5AE23EA46}">
   <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10506,7 +15815,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -11611,229 +16920,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37C4312A-7C4D-4B5B-9233-CE962B88EE09}">
-  <dimension ref="A1:K31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="21.88671875" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A1" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="5">
-        <v>6</v>
-      </c>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="13"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B15" s="14"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B16" s="14"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="14"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" s="14"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="14"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B21" s="15"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" s="5">
-        <v>19.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="5">
-        <v>77.599999999999994</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="5">
-        <v>78.900000000000006</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="5">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" s="5">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11904,7 +16990,7 @@
     </row>
     <row r="7" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B7" s="3">
         <f>AVERAGE(Cleaned_Data!K2:K31)</f>
